--- a/data/sample_input.xlsx
+++ b/data/sample_input.xlsx
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>day</t>
+          <t>days</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Tue, Thu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Mon, Wed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue, Thu</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1352,17 +1352,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon, Wed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5:30</t>
+          <t>3:45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">

--- a/data/sample_input.xlsx
+++ b/data/sample_input.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teams" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coaches" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NoDates" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Availability" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wishlist" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locals" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closures" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekends" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closures" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,10 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -53,9 +51,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,8 +418,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -432,199 +440,362 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>age</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>coach</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>head_coach</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>assistants</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>priority</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>weekend_only</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>weekend_pref</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12 Navy</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+          <t>12-Kai</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Girls</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>12</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Kai</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Eli</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>13 Navy</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+          <t>13-Marco</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Girls</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>13</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Eli</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Uma</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13 Black</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>13</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Marco</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
+          <t>14-Brooke</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Girls</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Brooke</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14 Navy</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Uma</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
+          <t>16-Rosa</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Girls</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rosa</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Dana</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>11/14/2026</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15 Navy</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>15</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Brooke</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
+          <t>17-Lena</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Girls</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>11/14/2026</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15 Black</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>15</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
+          <t>18-Ivy</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Girls</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ivy</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Quinn</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>11/14/2026</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16 Navy</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>16</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Rosa</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
+          <t>13 Black</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Boys</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Gabe</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17 Navy</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>17</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Kai</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>3</v>
-      </c>
+          <t>15 Black</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Boys</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Zoe</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Yara</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>17 Black</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>17</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Eli</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
+          <t>16 Black</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Boys</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Jude</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18 Navy</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+          <t>18 Black</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Boys</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>18</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Marco</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>3</v>
-      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Wes</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -637,206 +808,232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>coach</t>
+          <t>who</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>preferred_days</t>
+          <t>days</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>preferred_slots</t>
+          <t>dates</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>times</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kai</t>
+          <t>12-Kai</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>kai@example.com</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5:30</t>
+          <t>11/25</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tournament travel</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Eli</t>
+          <t>16-Rosa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eli@example.com</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mon, Tue</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>7:20</t>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Coach works late</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>16-Rosa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>marco@example.com</t>
+          <t>Not preferred</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mon, Fri</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Uma</t>
+          <t>17-Lena</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>uma@example.com</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>11/16-11/20</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>18-Ivy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>brooke@example.com</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thu, Fri</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>5:30</t>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Coach works late</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>18-Ivy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>carlos@example.com</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Tue, Wed</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>11/16</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rosa</t>
+          <t>13 Black</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rosa@example.com</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>11/25-11/27</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dana</t>
+          <t>18 Black</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dana@example.com</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Lena</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>lena@example.com</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Tue, Fri</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>5:30, 7:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Vic</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>vic@example.com</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>11/13-11/17</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -849,26 +1046,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>coach</t>
+          <t>team</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>choice</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>slot</t>
+          <t>days</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
+        <is>
+          <t>times</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -877,350 +1086,162 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dana</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="n">
-        <v>46329</v>
+          <t>13-Marco</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Wed, Fri</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Family</t>
-        </is>
-      </c>
+          <t>5:30</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brooke</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>46330</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
+          <t>14-Brooke</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Appointment</t>
-        </is>
-      </c>
+          <t>5:30</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kai</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>46330</v>
+          <t>16-Rosa</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Tue, Thu</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5:30</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lena</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>46332</v>
+          <t>17-Lena</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Mon, Wed, Fri</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Appointment</t>
-        </is>
-      </c>
+          <t>5:30</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Vic</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>46332</v>
+          <t>18-Ivy</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Mon, Wed</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Family</t>
-        </is>
-      </c>
+          <t>7:20</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dana</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>46336</v>
+          <t>13 Black</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Wed, Fri</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Appointment</t>
-        </is>
-      </c>
+          <t>5:30</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lena</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>46338</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
+          <t>15 Black</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tournament travel</t>
-        </is>
-      </c>
+          <t>7:20</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dana</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>46339</v>
+          <t>16 Black</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Mon, Wed, Fri</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Appointment</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Eli</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>46339</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Tournament travel</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Eli</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>46342</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Work</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Uma</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>46342</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>46343</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Uma</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>46343</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3:45</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Work</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>46344</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Appointment</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Eli</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>46346</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Appointment</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Brooke</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>46349</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Tournament travel</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Marco</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>46349</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Work</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Lena</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="n">
-        <v>46351</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>7:20</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Tournament travel</t>
-        </is>
-      </c>
+          <t>5:30</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1233,8 +1254,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1249,7 +1279,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>slot</t>
+          <t>time</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1260,13 +1290,23 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>coaches</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>on_site</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>dates</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Little Spikers (8-10U)</t>
+          <t>Girls HS League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1276,61 +1316,73 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3:45</t>
+          <t>5:30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dana</t>
-        </is>
-      </c>
+          <t>Yara; Lena</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Adult League</t>
+          <t>Boys 14 League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mon, Wed</t>
+          <t>Mon, Fri</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7:20</t>
+          <t>5:30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Carlos; Dana</t>
-        </is>
-      </c>
+          <t>Quinn; Rosa</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Skills Clinic</t>
+          <t>Boys HS League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tue, Thu</t>
+          <t>Mon, Fri</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5:30</t>
+          <t>7:20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1340,19 +1392,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Carlos; Brooke</t>
-        </is>
-      </c>
+          <t>Gabe</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Beginner Academy</t>
+          <t>Girls 14 League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mon, Wed</t>
+          <t>Wed, Fri</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1367,9 +1425,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marco</t>
-        </is>
-      </c>
+          <t>Ivy</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1382,8 +1446,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1393,13 +1465,141 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>courts</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>9AM-9PM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>11/14/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>9AM-9PM</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11/21/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>9AM-9PM</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>reason</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46352</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>11/26/2026</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1408,8 +1608,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46353</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>11/27/2026</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>

--- a/data/sample_input.xlsx
+++ b/data/sample_input.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -430,6 +430,7 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,6 +479,11 @@
           <t>weekend_pref</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>late_ok</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -511,6 +517,7 @@
           <t>AM</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -544,6 +551,7 @@
           <t>AM</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -577,6 +585,7 @@
           <t>AM</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -610,6 +619,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -643,6 +653,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -676,6 +687,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -709,6 +721,7 @@
           <t>AM</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -738,6 +751,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -767,6 +781,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -796,6 +811,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/sample_input.xlsx
+++ b/data/sample_input.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locals" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekends" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closures" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tournaments" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -431,6 +432,7 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -484,6 +486,11 @@
           <t>late_ok</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -518,6 +525,7 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -552,6 +560,7 @@
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -586,6 +595,7 @@
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -620,6 +630,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -654,6 +665,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -688,6 +700,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -722,6 +735,7 @@
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -752,6 +766,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -782,6 +797,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -812,6 +828,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1638,4 +1655,118 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ages</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>teams</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>program</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>courts</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Boys Travel Tournament</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>11/14/2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>11/15/2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Boys</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/sample_input.xlsx
+++ b/data/sample_input.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekends" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closures" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tournaments" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coaches" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1287,16 +1288,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1307,30 +1309,35 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>days</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>courts</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>coaches</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>on_site</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>dates</t>
         </is>
@@ -1342,32 +1349,33 @@
           <t>Girls HS League</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
         <is>
           <t>Tue, Thu</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>5:30</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>6-7</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Yara; Lena</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1375,32 +1383,33 @@
           <t>Boys 14 League</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Mon, Fri</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>5:30</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>6-7</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Quinn; Rosa</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1408,32 +1417,33 @@
           <t>Boys HS League</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Mon, Fri</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>7:20</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>6-7</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Gabe</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1441,32 +1451,33 @@
           <t>Girls 14 League</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Wed, Fri</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>3:45</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1-3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Ivy</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1769,4 +1780,46 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>